--- a/pruebas/macas_TVpromediostotal.xlsx
+++ b/pruebas/macas_TVpromediostotal.xlsx
@@ -796,11 +796,15 @@
       <c r="F9" s="7" t="n">
         <v>87.08</v>
       </c>
-      <c r="G9" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H9" s="7" t="n">
-        <v>0</v>
+      <c r="G9" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H9" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I9" s="7" t="n">
         <v>87.06999999999999</v>
@@ -817,11 +821,15 @@
       <c r="M9" s="7" t="n">
         <v>85.23</v>
       </c>
-      <c r="N9" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="O9" s="7" t="n">
-        <v>0</v>
+      <c r="N9" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O9" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="P9" s="7" t="n">
         <v>87.17</v>
@@ -904,11 +912,15 @@
       <c r="F10" s="7" t="n">
         <v>109.05</v>
       </c>
-      <c r="G10" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H10" s="7" t="n">
-        <v>0</v>
+      <c r="G10" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H10" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I10" s="7" t="n">
         <v>108.47</v>
@@ -925,11 +937,15 @@
       <c r="M10" s="7" t="n">
         <v>108.4</v>
       </c>
-      <c r="N10" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="O10" s="7" t="n">
-        <v>0</v>
+      <c r="N10" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O10" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="P10" s="7" t="n">
         <v>109.07</v>
@@ -1012,11 +1028,15 @@
       <c r="F11" s="7" t="n">
         <v>41.17</v>
       </c>
-      <c r="G11" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H11" s="7" t="n">
-        <v>0</v>
+      <c r="G11" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H11" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I11" s="7" t="n">
         <v>36.3</v>
@@ -1033,11 +1053,15 @@
       <c r="M11" s="7" t="n">
         <v>50.5</v>
       </c>
-      <c r="N11" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="O11" s="7" t="n">
-        <v>0</v>
+      <c r="N11" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O11" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="P11" s="7" t="n">
         <v>39.87</v>
@@ -1120,11 +1144,15 @@
       <c r="F12" s="7" t="n">
         <v>41.35</v>
       </c>
-      <c r="G12" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H12" s="7" t="n">
-        <v>0</v>
+      <c r="G12" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H12" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I12" s="7" t="n">
         <v>36.1</v>
@@ -1141,11 +1169,15 @@
       <c r="M12" s="7" t="n">
         <v>39.17</v>
       </c>
-      <c r="N12" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="O12" s="7" t="n">
-        <v>0</v>
+      <c r="N12" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O12" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="P12" s="7" t="n">
         <v>36.13</v>
@@ -1228,11 +1260,15 @@
       <c r="F13" s="7" t="n">
         <v>92.88</v>
       </c>
-      <c r="G13" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H13" s="7" t="n">
-        <v>0</v>
+      <c r="G13" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H13" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I13" s="7" t="n">
         <v>92.53</v>
@@ -1249,11 +1285,15 @@
       <c r="M13" s="7" t="n">
         <v>96.56999999999999</v>
       </c>
-      <c r="N13" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="O13" s="7" t="n">
-        <v>0</v>
+      <c r="N13" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O13" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="P13" s="7" t="n">
         <v>92.67</v>
@@ -1336,11 +1376,15 @@
       <c r="F14" s="7" t="n">
         <v>27.65</v>
       </c>
-      <c r="G14" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H14" s="7" t="n">
-        <v>0</v>
+      <c r="G14" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H14" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I14" s="7" t="n">
         <v>26.77</v>
@@ -1357,11 +1401,15 @@
       <c r="M14" s="7" t="n">
         <v>26.77</v>
       </c>
-      <c r="N14" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="O14" s="7" t="n">
-        <v>0</v>
+      <c r="N14" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O14" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="P14" s="7" t="n">
         <v>27.73</v>
@@ -1444,11 +1492,15 @@
       <c r="F15" s="7" t="n">
         <v>27.78</v>
       </c>
-      <c r="G15" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H15" s="7" t="n">
-        <v>0</v>
+      <c r="G15" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H15" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I15" s="7" t="n">
         <v>27.37</v>
@@ -1465,11 +1517,15 @@
       <c r="M15" s="7" t="n">
         <v>28.13</v>
       </c>
-      <c r="N15" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="O15" s="7" t="n">
-        <v>0</v>
+      <c r="N15" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O15" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="P15" s="7" t="n">
         <v>27.4</v>
@@ -1552,11 +1608,15 @@
       <c r="F16" s="7" t="n">
         <v>30.95</v>
       </c>
-      <c r="G16" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H16" s="7" t="n">
-        <v>0</v>
+      <c r="G16" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H16" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I16" s="7" t="n">
         <v>29.83</v>
@@ -1573,11 +1633,15 @@
       <c r="M16" s="7" t="n">
         <v>36.93</v>
       </c>
-      <c r="N16" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="O16" s="7" t="n">
-        <v>0</v>
+      <c r="N16" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O16" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="P16" s="7" t="n">
         <v>30.17</v>
@@ -1660,11 +1724,15 @@
       <c r="F17" s="7" t="n">
         <v>30.13</v>
       </c>
-      <c r="G17" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H17" s="7" t="n">
-        <v>0</v>
+      <c r="G17" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H17" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I17" s="7" t="n">
         <v>30.27</v>
@@ -1681,11 +1749,15 @@
       <c r="M17" s="7" t="n">
         <v>33.5</v>
       </c>
-      <c r="N17" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="O17" s="7" t="n">
-        <v>0</v>
+      <c r="N17" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O17" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="P17" s="7" t="n">
         <v>31.2</v>
@@ -1768,11 +1840,15 @@
       <c r="F18" s="7" t="n">
         <v>28.9</v>
       </c>
-      <c r="G18" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="H18" s="7" t="n">
-        <v>0</v>
+      <c r="G18" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H18" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I18" s="7" t="n">
         <v>28.7</v>
@@ -1789,11 +1865,15 @@
       <c r="M18" s="7" t="n">
         <v>29.67</v>
       </c>
-      <c r="N18" s="7" t="n">
-        <v>0</v>
-      </c>
-      <c r="O18" s="7" t="n">
-        <v>0</v>
+      <c r="N18" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O18" s="7" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="P18" s="7" t="n">
         <v>28.9</v>
@@ -1876,11 +1956,15 @@
       <c r="F19" s="10" t="n">
         <v>28.95</v>
       </c>
-      <c r="G19" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="H19" s="10" t="n">
-        <v>0</v>
+      <c r="G19" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H19" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="I19" s="10" t="n">
         <v>28.37</v>
@@ -1897,11 +1981,15 @@
       <c r="M19" s="10" t="n">
         <v>32.63</v>
       </c>
-      <c r="N19" s="10" t="n">
-        <v>0</v>
-      </c>
-      <c r="O19" s="10" t="n">
-        <v>0</v>
+      <c r="N19" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O19" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="P19" s="10" t="n">
         <v>31.6</v>
